--- a/光伏配储项目/电价数据/2026/水乡站.xlsx
+++ b/光伏配储项目/电价数据/2026/水乡站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.52799</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38465</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.7569199999999999</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.59396</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.5888600000000001</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.5268400000000001</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.5436</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.44051</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.45782</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.43005</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.42488</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.42412</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.41153</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.39944</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.39869</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.38676</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.40342</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.42629</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.41518</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.35508</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.39353</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.3868</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.41925</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.39401</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.42307</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.41617</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.42627</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.41401</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.44568</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.49839</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.30003</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.39923</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30827</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.31212</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.3282</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.35072</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.37541</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.32327</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.34174</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.10929</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.12002</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.28393</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.12821</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.05598</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.09875</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.27398</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>0.1507</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>0.30109</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.28488</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.05011</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>0.44011</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>0.65097</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.1459</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.21429</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.228</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.23414</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.21712</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>0.40237</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>0.11885</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.34115</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.13612</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.29592</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.30812</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.29289</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.27277</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.31857</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.53228</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.6315299999999999</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.49248</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.7330099999999999</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.04944</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.39494</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>0.74394</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.43217</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.43694</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.6592899999999999</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.7928099999999999</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.40149</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>1.12878</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>1.2594</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>0.96536</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>1.14534</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>1.21085</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.39074</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.36813</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.6123099999999999</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.665</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>1.37859</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>1.1076</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.86648</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.79698</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.75793</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.52093</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.47996</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.4734</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.41593</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.42561</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32887</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.71014</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.75862</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.86936</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.91384</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.49417</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.51585</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.50349</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.5037900000000001</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.48593</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.39982</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.46798</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.37841</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.37873</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.3822</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33637</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.36754</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.35296</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.35278</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.36745</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.37033</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.35354</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.376</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.41168</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.90185</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.7409199999999999</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.83231</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.45959</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.4411600000000001</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.37613</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.34767</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.38745</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.42737</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.50873</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.36661</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.34175</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.35709</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.34314</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.31592</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.3157799999999999</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.30036</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.33055</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.36677</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.49286</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.76439</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>0.97942</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.32225</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.5240499999999999</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.90652</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.8586</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.49992</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.70163</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>0.93951</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>1.07584</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>1.05904</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.28018</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.35665</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.36853</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.47342</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.53925</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.49014</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.5302100000000001</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.8872000000000001</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.6439400000000001</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.7808099999999999</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.80187</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>1.15855</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>1.25518</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>1.20662</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.86021</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>1.20351</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>1.1047</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>1.2588</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>1.0397</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>1.09001</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.64366</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>0.9829</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.90227</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>0.92825</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.7039800000000001</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>0.96857</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.79142</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.74096</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.45161</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.7843600000000001</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.8005</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.4496</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.42866</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.44446</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.33427</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.37598</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35493</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33465</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32142</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.5087</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.48665</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.49048</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.38678</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.45247</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.41564</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.37001</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.38953</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.38317</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.36346</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.42839</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.44394</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.33589</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.37033</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.39593</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.36726</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.36811</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35588</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.36138</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.35185</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.36473</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.35805</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.38418</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39563</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.47283</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.44449</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.43858</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.34745</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.39474</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35289</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.36734</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.3475</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.27601</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.27682</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.29949</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.36646</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.25846</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.22977</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.3075</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.3400899999999999</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.33027</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.34176</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.36106</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.37421</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.53808</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.47635</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0.8308</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.35667</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.57847</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.72609</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.81269</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.54799</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.50066</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.8189500000000001</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.72381</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.66172</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.6021299999999999</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.49397</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.42074</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.43129</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.40289</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.47014</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.49456</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.5086499999999999</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.56924</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.59315</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.5387000000000001</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.55865</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>1.27401</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.6177999999999999</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.58301</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.461</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.5067200000000001</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.53455</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.62425</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>0.5927899999999999</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.61534</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.34627</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.483</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.42485</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.48604</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.61222</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.6487200000000001</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.5631</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.7674800000000001</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.64364</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.5575399999999999</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.47805</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.61217</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.44242</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.45735</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.3979</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.36219</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.34861</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34201</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31894</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.5295800000000001</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.49152</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.45052</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.38835</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.38884</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.40145</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.36648</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.35838</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.38593</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.38433</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.35976</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.44937</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.35867</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.34785</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.36141</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.35642</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.35734</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.33675</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.33417</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.33043</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.33339</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.33028</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.34962</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33906</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.35129</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.38399</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.38876</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.34696</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.37348</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.34342</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.39229</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.41433</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.4255</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.35525</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.40726</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.33996</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.33977</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.27325</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.24251</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.35716</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.29027</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.25123</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.31011</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.60239</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.52552</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.44287</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.35401</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.21186</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.27569</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.43679</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.34085</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.35074</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.35326</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.43186</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.60263</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.36754</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.35597</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.32502</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.3511</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.48088</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.40159</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.39696</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.29209</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.31104</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.31887</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.46838</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.49469</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.42931</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.49613</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.44968</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.46277</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.39934</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.47497</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.51776</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.57625</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.44256</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.5568</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.46861</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.45615</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.4983</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.42159</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.4017</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.39465</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.41528</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.3440299999999999</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.36156</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.3461</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.34077</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.31904</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.32319</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.32054</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.31531</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.31854</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.3214</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.32051</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.41516</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.39209</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.38234</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.3613</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.34099</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.33072</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.3286</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.33346</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.32113</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.31924</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.31645</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.31956</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.31825</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.31517</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.31589</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.31425</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.31565</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.32113</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.31641</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.31184</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.31115</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.31351</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.31489</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31646</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32452</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32434</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.3326</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32612</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.32354</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.32609</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.33751</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.34912</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.37329</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.32935</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.28649</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.34662</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.34186</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.2999</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>0.31853</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>0.30377</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.32599</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>0.20396</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>0.31037</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>0.23394</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>0.22678</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>0.16131</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>0.30372</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>0.17501</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>0.28567</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>0.17367</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>-0.03878</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>0.0249</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0.396</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>0.39428</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.21903</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.17985</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.22223</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.05834</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>-0.03092</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>-0.02769</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>0.5408200000000001</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.28475</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.2981</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.30036</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.30811</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.2922</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.30075</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32957</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31546</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33545</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.33574</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.33587</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.33414</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.38077</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.38598</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.38086</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.37329</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.35828</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.39264</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.3948</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.40395</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.46322</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.37212</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.39227</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.39459</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.49069</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.3532</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35716</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.3445</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35427</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.34628</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.36717</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.61007</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.38626</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.41766</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.39885</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.39571</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.35498</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.34904</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.35326</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.31312</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.30388</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.29907</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.34088</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.29564</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.34304</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.34096</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.33086</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.29453</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.31868</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.31855</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.30436</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.29506</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.30179</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.33116</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.32636</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.33901</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.34785</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.32286</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.30923</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.10263</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.04349</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04699</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04573</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.0441</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04467</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04398</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>0.40183</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>0.02188</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.22884</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.06054</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>0.30882</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>0.2325</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>0.05065</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04392</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04395</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.0456</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04561</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04369</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04335</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04549</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04339</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.04529</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04525999999999999</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04538</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04359</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04423</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>0.08298999999999999</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>0.08127</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04471</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.04997</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.04983</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.0474</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04790999999999999</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.19975</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14272</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.28994</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29465</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30454</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.29982</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29492</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.29283</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.29329</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29226</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29678</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29074</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29497</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.26875</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29381</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.30855</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30375</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.30221</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.31434</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.31839</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.34731</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.34802</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.34173</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.3625</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.36169</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.33269</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.32637</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.31518</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31033</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.39825</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.34667</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.32045</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.30704</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31462</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30134</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28113</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29441</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29069</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.28802</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27116</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27089</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17236</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.1586</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17092</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.14769</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.15943</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15858</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23612</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.21399</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22651</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.26883</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28565</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29075</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.31932</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.28069</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28083</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.28102</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28043</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.27073</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28091</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32236</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31015</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30493</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.3163</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.30939</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.35894</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.31626</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.29736</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.38597</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.37966</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.42789</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.45591</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.33182</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.41846</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.4153</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.38787</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.40243</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.30005</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30095</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.2993</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.29998</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15653</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.29434</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31094</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.31343</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.3127200000000001</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32184</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34629</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30067</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.33083</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.38546</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.5076700000000001</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79098</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.6220399999999999</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78528</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.40003</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49798</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.7810199999999999</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.92039</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.49456</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.91422</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.86291</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.29624</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.35369</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.88754</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.63161</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.18712</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.8674299999999999</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.44965</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.33089</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.03294</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.5308200000000001</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.79101</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.50483</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.773</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.7775700000000001</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.8767699999999999</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.87388</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.49318</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.3987</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.39993</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.44997</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.20703</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87883</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55102</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.62188</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.5383300000000001</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.4977</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45582</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42426</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.43715</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.44978</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.38818</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45268</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.41973</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.34855</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.39895</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.36355</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.38399</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.41093</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.42878</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.34103</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.38797</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.34735</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.33683</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.33024</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.34177</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.39057</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.34747</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.44975</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.349</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.39503</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.38912</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.5676100000000001</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.41873</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.5884199999999999</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.7169</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.87738</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.46768</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.40035</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.56132</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.43967</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.83563</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.58804</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.85827</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.87495</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.34262</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.42404</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.6501699999999999</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.33113</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.3038</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.29713</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.66715</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.60187</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.2395</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.3106</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.3542</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.33117</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.3208</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.4064700000000001</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.33519</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.3174</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.31954</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.31909</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.31956</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.33847</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.31631</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.31091</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.31922</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.30217</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.29578</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.31163</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.31104</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.31118</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.29629</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.30348</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.30769</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.31596</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.31473</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.31856</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.35016</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.33381</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.3361</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.33399</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.32629</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.33136</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.32954</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.39512</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.39743</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.43252</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.39949</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.37962</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.36327</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.3493</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32835</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.9149700000000001</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.35317</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.45082</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.42073</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.39841</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.44609</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.37122</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.39641</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.35494</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.3584</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.34339</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.34243</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.33877</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.32647</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.35189</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.3395</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.31923</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.38498</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.47429</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.34974</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.37507</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.33709</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.3434700000000001</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.34721</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.36051</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.34991</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.3547</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.31091</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.31069</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.32764</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.33286</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.33348</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.34382</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.31338</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.31173</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.28944</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.31347</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.30512</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.30011</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.18211</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.30445</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.30833</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.33792</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.33558</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.35299</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.31154</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.27342</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.19839</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.30648</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.29861</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.32138</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.28331</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.31039</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.31083</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.3507</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.35885</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.3114</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.30588</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.31454</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.31704</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.32868</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.31405</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.30408</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.29956</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.30452</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.31343</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.31042</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.28934</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.34134</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.25475</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.34231</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.31614</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.32859</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.332</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.27552</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.34137</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.32388</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.33337</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.30492</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.3425</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.33131</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.34366</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.42249</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.3433</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.33309</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.42183</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.34771</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.44407</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.33081</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.40741</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.35422</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.38764</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.3857</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.55433</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.33106</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.87613</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.46617</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.14866</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.6924400000000001</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.7829700000000001</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.64347</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.53035</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.41761</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.44453</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.49469</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.43438</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.42399</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.40935</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.4079100000000001</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.41126</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.47544</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.40802</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.42894</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.39707</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.42926</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.38631</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.40906</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.4285</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.39144</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.41896</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.41476</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.4080299999999999</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.40911</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.38518</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.40398</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.39358</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.38674</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.48975</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.35886</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.32041</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.29115</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.35276</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.36047</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.30748</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.33682</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.30557</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.31301</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.30085</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.53477</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.35969</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.25469</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.24907</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.29595</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.16161</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.27686</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.27643</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>0.005860000000000001</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.33707</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.30122</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.26077</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.25425</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.30772</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.28245</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.28787</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.29713</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.29027</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.30689</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.31191</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.32061</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.32269</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.31263</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.33294</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.33387</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.39328</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.38987</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.34661</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.35554</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.33564</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.32651</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.36306</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.33706</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.35079</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.3583</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.35739</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.34421</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.5520900000000001</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.44309</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.80371</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.44449</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.41881</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.36902</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.45164</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.37514</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.36013</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.32758</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.32955</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.32298</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.3131</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.3183</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.40049</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.32616</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.32949</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.31321</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.33062</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.30521</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.30873</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.30427</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.30449</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.29868</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.29761</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.31549</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.31392</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.31399</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.31006</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.29461</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.29462</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.30398</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.31886</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.30553</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.26787</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.29933</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.36256</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.27248</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.32759</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.3694</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.3465299999999999</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.3369</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.33301</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.33702</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.32251</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.30941</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.3142200000000001</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.25313</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.32679</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.28776</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.27258</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.28589</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.26708</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.22859</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.148</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.13581</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.27402</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.13774</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.1445</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.13936</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.25162</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.13633</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.24784</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.13988</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.24912</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.27885</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.20713</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.12682</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.10577</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.10904</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.13015</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.19754</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.14323</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.26819</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.3144</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.2972</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.31014</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.33448</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.31833</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.34539</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.33499</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.34141</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.33692</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.36891</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.34056</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.38562</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.35083</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.37187</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.42773</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.38472</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.37737</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.38614</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.38312</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.43085</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.41878</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.41883</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.42339</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.43973</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.39727</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.38534</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.39274</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.3866</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.34852</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.34933</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.33354</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.33914</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.33198</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.5065299999999999</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.38443</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.44618</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.40724</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.40018</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.36013</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.36982</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.36843</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.38034</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.37529</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.36584</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.37044</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.35249</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.37962</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.36112</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.36883</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.34259</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.33999</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.34736</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.33786</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.3337</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.33824</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.3337</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.3432</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.42942</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.35988</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.3693</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.35177</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.33472</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.33347</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.33491</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.32331</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.33638</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.34314</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.35682</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.2957</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.31063</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.31195</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.30548</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.29366</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.28775</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.27291</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.27081</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.23298</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.30623</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.26643</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.24919</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.2819</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.30087</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.30136</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.3181</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.31788</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.32316</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.36932</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.3136</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.3227</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.2954</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.23936</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.31439</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.30481</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.3221</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.32347</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.30243</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.43706</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.34142</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.3749</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.34789</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.33635</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.3358</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.42818</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.37732</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.34891</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.34369</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.34905</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.36765</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.39175</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.38019</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.39104</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.2666</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.3782799999999999</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.37486</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.35211</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.35179</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.34924</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.40844</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.34266</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.34597</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.36266</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.36252</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.35553</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.36726</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.3706</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.37479</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.3435299999999999</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.35244</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.33709</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.3577</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.47495</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.36627</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.48714</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.37056</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.3457</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.35836</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.35039</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.34235</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.33456</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.33992</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.33875</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.34236</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.34241</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.34164</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.33671</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.3352</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.33859</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.33405</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.33175</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.33539</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.33139</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.33405</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.33825</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.34226</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.36804</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.3757</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.3779</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.36607</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.32919</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.33711</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.32739</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.34574</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.38254</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>1.27549</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.34184</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.63493</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.33888</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.42345</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.40967</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.31945</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.3822</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.49502</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.35408</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.38094</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.39021</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.5016700000000001</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.22921</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.26529</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.48532</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.265</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.56431</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.37877</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.33846</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.86533</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.34829</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.29197</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.3049</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.30129</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.30219</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.45917</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.33509</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.39019</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.36181</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.41155</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.37001</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.33769</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.38137</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.34708</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.31208</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.40532</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.32664</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.32265</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.66938</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.44935</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.36981</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.43041</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.41259</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.68647</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.35853</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.6918500000000001</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.6349400000000001</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.5394600000000001</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.37034</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.5060899999999999</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.24409</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.37279</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.35304</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.33331</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.33256</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.33927</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.32108</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.34954</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.29439</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.32574</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.31999</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.34583</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.40968</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.42364</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.34527</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.32717</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.34092</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.36031</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.32625</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.311</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.32717</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.33671</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.32304</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.32291</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.32226</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.31945</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.31369</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.3212</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.31121</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.30186</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.30869</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.3157</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.31887</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.31743</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.31095</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.31569</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.32706</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.32981</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.3249</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.31028</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.33148</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.3192</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.33599</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>1.35154</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>1.37535</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>1.37446</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.5954400000000001</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.60936</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.37228</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>1.34588</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>1.32192</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.7005399999999999</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.63513</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.61041</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.5624</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.59763</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.52206</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.33013</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.27933</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.32866</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.31423</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.31584</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.32116</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.32356</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.33022</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.33432</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.32376</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.32112</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.31188</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.31357</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.31487</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.31297</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.3423</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.33532</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.38525</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.60862</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.42464</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.42396</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.42466</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.42563</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.34495</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.3435</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.34304</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.33766</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.32474</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.31381</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.3396</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.41091</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.35653</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.34844</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.34623</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.34962</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.35265</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.35446</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.36463</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.37225</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.7973899999999999</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.80462</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.35068</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.36572</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.35797</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.33928</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.32403</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.34585</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.33332</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.34545</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.33301</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.34623</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.34521</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.34622</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.3472</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.34665</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.34586</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.33987</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.34523</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.34208</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.30726</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.34286</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.33882</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.34055</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.32818</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.33541</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.33586</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.33207</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.35727</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.3202</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.33059</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.3354</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.34029</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.3295</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.33033</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.34086</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.32867</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.34113</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.34106</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.33219</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.33179</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.32075</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.33956</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.3338</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.32369</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.32936</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.30337</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.32153</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.32436</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.32636</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.3235</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.31601</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.32418</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.31525</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.31582</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.32502</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.32268</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.32798</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31693</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.36906</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.3246</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.31884</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.34379</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.38294</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.32856</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.34214</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.3343</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.32641</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.32697</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.33779</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.34327</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.335</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.3349</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.34237</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.35355</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.35421</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.35088</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.34961</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.35544</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.36218</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.34566</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.35345</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.34162</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.35276</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.35458</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.35666</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.3445299999999999</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.37465</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.36831</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.37208</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.37623</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.41137</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.40742</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.37133</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.37162</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.6526799999999999</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.7141000000000001</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.43699</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.26533</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.43948</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.40762</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.3462</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.37087</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.3551</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.33551</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.33789</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.3222</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.40686</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.37199</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.36403</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.35774</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.35489</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.35455</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.35772</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.35383</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.35384</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.35468</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.34854</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.35569</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.35344</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.35183</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.34778</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.35241</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.35518</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.3555</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.34348</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.35834</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.35448</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.35221</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.35577</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.35577</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.369</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.36158</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.37559</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.35226</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.35218</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.34688</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.34757</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.35363</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.34499</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.32667</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.30349</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.32753</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.31112</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.26495</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.15303</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.29775</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.28849</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.2967</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.21469</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.25666</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.32515</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.32697</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.28619</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.2293</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.2638</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.29049</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.28328</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.30374</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.2936</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.30522</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.30582</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.37467</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.32214</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.30735</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.30308</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.34289</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.31154</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.33112</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.31764</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.32368</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.33324</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.33137</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.31014</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.33337</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.35222</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.34046</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.34194</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.31836</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.32815</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.3991</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.3449</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.40726</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.63967</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.5978300000000001</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.60075</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.45788</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.80292</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.4564</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>0.7362799999999999</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.39978</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.4855</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.39685</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.35759</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.3309</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.44648</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.41418</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.40442</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.37016</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.37051</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.35997</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.3535</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.34586</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.46688</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.54538</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.48849</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.64239</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.40313</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.40342</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.39103</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.39676</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.39569</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.4026</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.38771</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.39037</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.39948</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.39764</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.38468</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.38361</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.40352</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.37687</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.40185</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.37893</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.38417</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.38643</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.39817</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.38497</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.42663</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.42761</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.5229</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.47342</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.43094</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.47175</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.42934</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.50012</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.3927</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.37662</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.43981</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.47625</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.46871</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.5558099999999999</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.42999</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.36908</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.35014</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.35837</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.38995</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.38947</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.40892</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.35922</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.35619</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.29642</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.32796</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.31916</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.39868</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.6474500000000001</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.4134</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.97948</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.37217</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.36903</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.39287</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.36826</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.34592</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.33876</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.31269</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.33378</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.35094</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.3397</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.36212</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.35424</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.36023</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.36508</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.37564</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.34747</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.37093</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.33407</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.39929</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.42076</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.46944</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.42986</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.48338</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.48435</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.51923</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.6467000000000001</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.76423</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>0.8436699999999999</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.59049</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.74337</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.637</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.5001</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.7657</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.7668700000000001</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.6196699999999999</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.66835</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.43055</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.45343</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.45941</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.45505</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.44814</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.40384</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.52088</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.41296</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.42474</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.43642</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.43017</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.42007</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.4273</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.41182</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.38683</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.42829</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.38181</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.38849</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.37989</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.37499</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.36883</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.36334</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.35582</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.35262</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.3616</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.32263</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.3576</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.34929</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.3555</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.3616</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.37063</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.37496</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.37518</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.35567</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.35703</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.3508</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.37511</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.39702</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.36257</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.38312</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.39473</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.38456</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.38216</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35125</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.36311</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.34133</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.33511</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.34234</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.37123</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.23498</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.38267</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.35886</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0.34086</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>0.07598999999999999</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.3654</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.35425</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.40771</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.36606</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.44583</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.40262</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.45943</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.34137</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.32103</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.13976</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.20862</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.29387</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.29784</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.32163</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.34632</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.34086</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.34198</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.34317</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.36256</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.38337</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.38467</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.37652</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.40304</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.34911</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.42786</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.41311</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.43281</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.40381</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.40053</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.3627</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.36669</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.38514</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.39035</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.33345</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.35096</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.37167</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.37931</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.35581</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.36719</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.35738</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.38374</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.35267</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.36356</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.3322</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.36651</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.35259</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.34362</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.30926</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.47308</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.35431</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.38544</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.37045</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.34803</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.35651</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.32429</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.32442</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.34299</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.30698</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.30412</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.3242</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.30582</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.32541</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.3471</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.32332</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.29078</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.30644</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.31451</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.31973</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.31018</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.31486</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.31954</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.28254</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.32421</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.28152</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.27799</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.34295</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.29853</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.29487</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.31117</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.27504</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.34581</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.31693</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.30931</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.30838</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.19944</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.28398</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.24023</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.2770899999999999</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.25776</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.2546</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.10944</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.32056</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.30864</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.29039</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.25468</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.03724</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.29076</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.28112</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.18624</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.20591</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.30946</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.31284</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.30853</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.24417</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.26505</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.25972</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.23797</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.27621</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.28481</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.27872</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.32531</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.32853</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.32063</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.34424</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.34074</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.3484</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.3703</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.34616</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.34556</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.32037</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.3722200000000001</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.38853</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.34796</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.30562</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.3644</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.34629</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.36324</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.34088</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.35272</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.37274</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.34769</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.33199</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.35303</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.3671</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.32839</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.3473</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.34115</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.35254</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.33475</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.32205</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.33768</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.32207</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.3328</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.30829</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.32206</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.3326</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.33225</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.335</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.329</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.29261</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.30375</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.29916</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.3103</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.26347</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.29439</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.30071</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.29714</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.27005</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.26367</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.26549</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.26548</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.26199</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.26199</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.26408</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.28999</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.25949</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.26199</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.26233</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.29142</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.26383</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.2636</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.32644</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.26781</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.17897</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.2668</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.22736</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.01446</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.00045</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>-0.00115</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.04956</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.14574</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>0.02006</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.03956</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.04958</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.01518</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.04268</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.04052</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.04855</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.04819</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.02447</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.02904</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.04958</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.04959</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.04938</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>0.00029</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.27189</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.04963</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.04929</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.04959</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.03915</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.01865</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.04957</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.03629</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.20047</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.26297</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.28709</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.2795</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.30554</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.3088</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.26544</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.31193</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.33042</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.34487</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.33756</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.342</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.31069</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.31639</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.35203</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.34055</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.34554</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.34014</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.33905</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.34635</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.34088</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.36691</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.42481</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.35389</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.3698</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.34954</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.34423</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.34512</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.3368</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.34449</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.30171</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.33046</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29801</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.75014</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.6273099999999999</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.38644</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.45615</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.39779</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.41932</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.42308</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.36508</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.34414</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.33674</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.31807</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.32973</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.32454</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.31271</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.31702</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.29493</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.32553</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.26591</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.30144</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.29273</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.32125</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.28819</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.30847</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.32044</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.34633</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.43564</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.36997</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.3444700000000001</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.34562</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.28917</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.37183</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>0.72761</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.87052</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.8718400000000001</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.8336</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.32069</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.37913</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.1057</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.22353</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.29073</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.29517</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.28389</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.28564</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.25753</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.29396</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.34843</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.23305</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.25609</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>-0.00337</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.26199</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>-0.0026</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.30494</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.31089</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.27941</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>0.05496</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.27198</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.29312</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.2764</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.29371</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.25485</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.29204</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.46948</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.32105</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.3262</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.34821</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.38097</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.39362</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.34798</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.37339</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.36312</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.39528</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>1.55909</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.8093899999999999</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.78844</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.79547</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>1.37985</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.98256</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.7890499999999999</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.8495</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.81984</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.84172</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.83987</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.84429</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.94135</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.78265</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.8157300000000001</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.78488</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.37099</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.35864</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.37424</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.36841</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.36824</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33007</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.47717</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.63139</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.7125499999999999</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.59161</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.49465</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.47423</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.41154</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.40227</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.38263</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.38189</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.37045</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.33861</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.34398</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.33317</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.3283</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.5108199999999999</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.33169</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.32925</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.32641</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.31959</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.32469</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.30938</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.36058</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.35481</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.37837</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.47561</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.4899</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.37882</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.39607</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.32442</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.32908</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.33731</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.4297</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.37818</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.46843</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.36759</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.41704</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.40527</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.35814</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.35222</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.33447</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.3989</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.3493</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.31647</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.32936</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.33712</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.31238</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.26321</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.31524</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.30624</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.30648</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.32687</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.32462</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.32205</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.35507</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.31846</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.32975</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.31533</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.31758</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.32206</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.33884</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.34165</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.33004</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.33234</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.3265</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.34596</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.34905</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.34656</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.35806</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.34728</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.35538</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.33445</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.36442</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.40217</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.39386</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.38023</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.34841</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.37917</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.37654</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.42933</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.47014</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.7868999999999999</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.41804</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.6314099999999999</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.47623</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.38736</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.43624</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.42753</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.40286</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.49956</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.36074</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.36652</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.3482</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.35127</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.34698</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.43043</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.43605</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.41854</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.40145</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.39358</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.38922</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.38534</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.36377</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.36786</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.36002</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.35933</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.34982</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.35353</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.35236</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.34537</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.36038</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.3435</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.34257</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.33733</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.3383</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.33962</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.3397</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.35068</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.34232</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.3592</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.35165</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.3599</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.35154</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.36191</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.42649</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.37603</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.36523</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.59363</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.79016</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.57701</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.52088</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.5899800000000001</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.47045</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.36675</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.35987</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.35126</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.35003</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.35954</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.3477</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.35727</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.39158</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.35301</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.30518</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.33804</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.31661</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.33162</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.29808</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.33012</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.3431</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.34999</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.32635</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.32429</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.31404</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.33074</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.32955</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.33413</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.32357</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.34898</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.34771</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.40222</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.39295</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.47617</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0.45831</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.80532</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.42708</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.41207</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>0.45786</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.53532</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.48872</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.8198200000000001</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.4581</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.7504500000000001</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.5910700000000001</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.47828</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.47811</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.41862</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.37517</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.39855</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.35858</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.36845</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.35665</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.43713</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.3886</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.36173</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.39013</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.37079</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.24203</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.36329</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.35151</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.35943</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.34177</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.46445</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.39013</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.38811</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.37967</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.37406</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.35274</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.36501</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.36927</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.36886</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.36727</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.3595</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.35795</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.35366</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.35155</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.35292</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.35251</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.34658</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.3228</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.34706</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.34129</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.33915</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.3379</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.34445</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.34886</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.35866</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.38378</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.36231</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.36009</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.35053</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.35491</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.35377</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.35466</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.3851</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.39183</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.36975</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.35441</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.43574</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.38059</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.36644</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.38248</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.35945</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.31069</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.36366</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.27655</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.36932</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.35452</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.35235</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.29254</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.31554</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.32701</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.33625</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.31373</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.31602</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.33641</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.34356</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.32529</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.3337</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.34217</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.33863</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.32496</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.34432</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.3444700000000001</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.37498</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.3701</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.37559</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.36556</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.38055</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.39772</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.37705</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.37789</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.42211</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.41882</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.5260900000000001</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.5835399999999999</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>0.62686</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.58828</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.7557</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.6582100000000001</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.49086</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.5585399999999999</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.64699</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.49193</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.7783099999999999</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.78286</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>0.98993</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.86607</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.80145</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.80513</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.38611</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.43526</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.38707</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.36565</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.3692</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.35903</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.36378</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.30573</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.36301</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.36198</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.35626</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.35237</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.34334</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.33589</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.34602</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.34012</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.33946</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.34636</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.32956</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.37821</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.346</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.33604</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.34688</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.3424</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.28363</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.33204</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.33487</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.34075</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.3358</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.33618</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.34828</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.35385</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.34927</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.37887</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.37747</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.35497</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.34597</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.34321</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.34185</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.37291</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.33646</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.35246</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.35846</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.33818</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.34826</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.33532</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.17296</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.27035</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.2919</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.17232</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>0.33082</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.32817</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>0.20127</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0.21522</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.22225</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.15312</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.04238</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.29528</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.26439</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.16341</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.37587</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.10762</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.10486</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.22288</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.10066</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.29138</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.22488</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.17883</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.20193</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.31044</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.3470299999999999</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.34149</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.31821</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.35855</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.36633</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.35047</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.36588</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.35041</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.35615</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.37118</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.37438</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.3625</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.36266</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.35253</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.38454</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.4674700000000001</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.40944</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.39594</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.4523</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.43944</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.40006</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.3897</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.42256</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.38996</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.37664</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.40454</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.37131</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.41662</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.3747200000000001</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.36869</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.35238</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.35024</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.37019</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.3422</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0.9677899999999999</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.38701</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.59926</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.50313</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.39481</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.36981</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.46469</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.37338</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.39155</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.37466</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.3716</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.37436</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.37201</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.36747</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.37431</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.37152</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.36928</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.3702</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.36649</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.36088</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.3671</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.36555</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.36399</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.36285</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.35378</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.35988</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.35616</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.37485</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.35962</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.3474</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.35005</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.35556</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.36248</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.36421</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.35808</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.34264</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.38018</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.36596</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.36308</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.36611</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.28222</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.36588</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.3718</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.37395</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.5261</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.33458</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.38901</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>0.34076</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.33761</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.38467</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.36704</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.40899</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.39755</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.39338</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.48283</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.36332</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.32001</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.35925</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.34721</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.32354</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.36082</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.33381</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.35803</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.34897</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.35603</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.38491</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.38064</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.42831</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.40987</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.39857</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.35906</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.36778</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.38667</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.37926</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.35719</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.36156</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.37499</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.37156</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.37894</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.3877</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.37254</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.38875</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.37073</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.39798</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.35676</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.36847</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.41049</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.37902</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.38623</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.34681</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.36086</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.36054</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.36156</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.36243</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.34775</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.41402</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.38798</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.37814</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.37005</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.37903</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.37748</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.37161</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.37361</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.36348</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.3718399999999999</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.3608</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.36263</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.36402</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.35912</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.36588</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.35224</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.36001</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.36171</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.36182</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.35685</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.35763</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.35923</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.35802</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.36073</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.35232</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.3445299999999999</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.35806</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.35125</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.3523</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.31257</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.31465</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.32237</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.17438</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.30942</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.29237</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.30819</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.14411</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.19624</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.14122</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.30075</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.04221</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.12895</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.34053</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.23917</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.29337</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.16726</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.1473</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.3119</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.21366</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.32364</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.2241</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.26063</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.15245</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.35024</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.30494</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.14711</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.35201</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.29031</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.19542</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.14268</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.27846</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.2481</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.32193</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.31877</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.3082</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.30579</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.3439700000000001</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.35023</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.36365</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.35162</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.35556</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.35938</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.38433</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.36764</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.36106</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.35604</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.37041</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.36054</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.37173</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.37408</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.35768</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.37765</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.39193</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.38464</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.37546</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.39782</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.4706</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.39371</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.39038</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.38444</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.3902</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.37649</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.38159</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.38667</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.38673</v>
       </c>
     </row>
   </sheetData>
